--- a/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-activite-cisis.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-activite-cisis.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085853</t>
+    <t>20260916095456</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:53+01:00</t>
+    <t>2026-09-16T09:54:56+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,42 +100,12 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>PAT-040</t>
-  </si>
-  <si>
-    <t>Activité salariée</t>
-  </si>
-  <si>
-    <t>PAT-042</t>
-  </si>
-  <si>
-    <t>Retraité</t>
-  </si>
-  <si>
     <t>PAT-043</t>
   </si>
   <si>
     <t>Au foyer</t>
   </si>
   <si>
-    <t>PAT-044</t>
-  </si>
-  <si>
-    <t>Congé parental</t>
-  </si>
-  <si>
-    <t>PAT-045</t>
-  </si>
-  <si>
-    <t>Chômeur</t>
-  </si>
-  <si>
-    <t>PAT-046</t>
-  </si>
-  <si>
-    <t>Elève, étudiant ou en formation</t>
-  </si>
-  <si>
     <t>GEN-092.05.06</t>
   </si>
   <si>
@@ -154,6 +125,39 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>224363007</t>
+  </si>
+  <si>
+    <t>employé(e)</t>
+  </si>
+  <si>
+    <t>105493001</t>
+  </si>
+  <si>
+    <t>retraité(e)</t>
+  </si>
+  <si>
+    <t>700149001</t>
+  </si>
+  <si>
+    <t>en congé parental</t>
+  </si>
+  <si>
+    <t>73438004</t>
+  </si>
+  <si>
+    <t>sans emploi</t>
+  </si>
+  <si>
+    <t>65853000</t>
+  </si>
+  <si>
+    <t>étudiant</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -417,7 +421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -461,55 +465,93 @@
         <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>36</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
